--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.88573006206227</v>
+        <v>4.693931135085118</v>
       </c>
       <c r="D2" t="n">
-        <v>29.00489715861632</v>
+        <v>4.713295788275152</v>
       </c>
       <c r="E2" t="n">
-        <v>8.679925474557308</v>
+        <v>1.410487889615563</v>
       </c>
       <c r="F2" t="n">
-        <v>8.711584327975906</v>
+        <v>1.415632453296085</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.0371289936224</v>
+        <v>4.881033461463641</v>
       </c>
       <c r="D3" t="n">
-        <v>30.19834411389502</v>
+        <v>4.907230918507941</v>
       </c>
       <c r="E3" t="n">
-        <v>8.679925474557308</v>
+        <v>1.410487889615563</v>
       </c>
       <c r="F3" t="n">
-        <v>8.711584327975906</v>
+        <v>1.415632453296085</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.87503691414473</v>
+        <v>5.667193498548519</v>
       </c>
       <c r="D4" t="n">
-        <v>34.87962449484404</v>
+        <v>5.667938980412156</v>
       </c>
       <c r="E4" t="n">
-        <v>8.679925474557308</v>
+        <v>1.410487889615563</v>
       </c>
       <c r="F4" t="n">
-        <v>8.711584327975906</v>
+        <v>1.415632453296085</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.6279028504166</v>
+        <v>8.227034213192699</v>
       </c>
       <c r="D5" t="n">
-        <v>50.83001098961946</v>
+        <v>8.259876785813162</v>
       </c>
       <c r="E5" t="n">
-        <v>8.679925474557308</v>
+        <v>1.410487889615563</v>
       </c>
       <c r="F5" t="n">
-        <v>8.711584327975906</v>
+        <v>1.415632453296085</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
